--- a/salidas/empresas/REGN.xlsx
+++ b/salidas/empresas/REGN.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,54 +447,54 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
@@ -501,7 +513,7 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>16.47453498840332</v>
+        <v>16.47453308105469</v>
       </c>
       <c r="C4" t="n">
         <v>16.6299991607666</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.38426113128662</v>
+        <v>14.3842601776123</v>
       </c>
       <c r="C5" t="n">
         <v>14.52000045776367</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.81902980804443</v>
+        <v>12.81902885437012</v>
       </c>
       <c r="C6" t="n">
         <v>12.9399995803833</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>12.70015144348145</v>
+        <v>12.70015239715576</v>
       </c>
       <c r="C7" t="n">
         <v>12.81999969482422</v>
@@ -596,11 +608,11 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.53229904174805</v>
+        <v>13.53229999542236</v>
       </c>
       <c r="C8" t="n">
         <v>13.65999984741211</v>
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>15.73154640197754</v>
+        <v>15.73154735565186</v>
       </c>
       <c r="C9" t="n">
         <v>15.88000011444092</v>
@@ -634,7 +646,7 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>19.86256217956543</v>
+        <v>19.8625602722168</v>
       </c>
       <c r="C11" t="n">
         <v>20.04999923706055</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>19.88237762451172</v>
+        <v>19.88237380981445</v>
       </c>
       <c r="C13" t="n">
         <v>20.06999969482422</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>19.70405769348145</v>
+        <v>19.70405387878418</v>
       </c>
       <c r="C14" t="n">
         <v>19.88999938964844</v>
@@ -729,7 +741,7 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
@@ -748,7 +760,7 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>26.94572257995605</v>
+        <v>26.94572067260742</v>
       </c>
       <c r="C17" t="n">
         <v>27.20000076293945</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>22.23022079467773</v>
+        <v>22.2302188873291</v>
       </c>
       <c r="C18" t="n">
         <v>22.44000053405762</v>
@@ -805,11 +817,11 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>17.75247573852539</v>
+        <v>17.75247383117676</v>
       </c>
       <c r="C19" t="n">
         <v>17.92000007629395</v>
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.75080108642578</v>
+        <v>14.75080013275146</v>
       </c>
       <c r="C20" t="n">
         <v>14.89000034332275</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>19.27807807922363</v>
+        <v>19.278076171875</v>
       </c>
       <c r="C21" t="n">
         <v>19.45999908447266</v>
@@ -862,11 +874,11 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>17.63359451293945</v>
+        <v>17.63359832763672</v>
       </c>
       <c r="C22" t="n">
         <v>17.79999923706055</v>
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>21.57639122009277</v>
+        <v>21.57638931274414</v>
       </c>
       <c r="C24" t="n">
         <v>21.78000068664551</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>23.92423248291016</v>
+        <v>23.92423439025879</v>
       </c>
       <c r="C25" t="n">
         <v>24.14999961853027</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>20.09041023254395</v>
+        <v>20.09041213989258</v>
       </c>
       <c r="C26" t="n">
         <v>20.28000068664551</v>
@@ -957,7 +969,7 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
@@ -976,7 +988,7 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
@@ -995,7 +1007,7 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>19.71396446228027</v>
+        <v>19.71396255493164</v>
       </c>
       <c r="C30" t="n">
         <v>19.89999961853027</v>
@@ -1033,7 +1045,7 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>21.68535804748535</v>
+        <v>21.68535995483398</v>
       </c>
       <c r="C32" t="n">
         <v>21.88999938964844</v>
@@ -1071,7 +1083,7 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
@@ -1090,7 +1102,7 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
@@ -1109,7 +1121,7 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
@@ -1128,7 +1140,7 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>18.18836402893066</v>
+        <v>18.18836212158203</v>
       </c>
       <c r="C37" t="n">
         <v>18.36000061035156</v>
@@ -1166,7 +1178,7 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>14.11678504943848</v>
+        <v>14.11678314208984</v>
       </c>
       <c r="C39" t="n">
         <v>14.25</v>
@@ -1204,7 +1216,7 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
@@ -1223,7 +1235,7 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>15.1272497177124</v>
+        <v>15.12724876403809</v>
       </c>
       <c r="C42" t="n">
         <v>15.27000045776367</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.75247573852539</v>
+        <v>17.75247383117676</v>
       </c>
       <c r="C43" t="n">
         <v>17.92000007629395</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1299,7 +1311,7 @@
       <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
@@ -1318,7 +1330,7 @@
       <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1337,11 +1349,11 @@
       <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>15.55322742462158</v>
+        <v>15.55322933197021</v>
       </c>
       <c r="C47" t="n">
         <v>15.69999980926514</v>
@@ -1356,7 +1368,7 @@
       <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
@@ -1375,11 +1387,11 @@
       <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.95395278930664</v>
+        <v>23.95395660400391</v>
       </c>
       <c r="C49" t="n">
         <v>24.18000030517578</v>
@@ -1394,7 +1406,7 @@
       <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
@@ -1413,11 +1425,11 @@
       <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.23133277893066</v>
+        <v>24.23133659362793</v>
       </c>
       <c r="C51" t="n">
         <v>24.45999908447266</v>
@@ -1432,7 +1444,7 @@
       <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
@@ -1451,7 +1463,7 @@
       <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
@@ -1470,11 +1482,11 @@
       <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>28.30291366577148</v>
+        <v>28.30291175842285</v>
       </c>
       <c r="C54" t="n">
         <v>28.56999969482422</v>
@@ -1489,11 +1501,11 @@
       <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>22.11133766174316</v>
+        <v>22.11134147644043</v>
       </c>
       <c r="C55" t="n">
         <v>22.31999969482422</v>
@@ -1508,11 +1520,11 @@
       <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.9638614654541</v>
+        <v>23.96385955810547</v>
       </c>
       <c r="C56" t="n">
         <v>24.19000053405762</v>
@@ -1533,11 +1545,11 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>21.77452087402344</v>
+        <v>21.7745189666748</v>
       </c>
       <c r="C57" t="n">
         <v>21.97999954223633</v>
@@ -1558,7 +1570,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
@@ -1583,7 +1595,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
@@ -1608,7 +1620,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
@@ -1633,7 +1645,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1658,11 +1670,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>33.36513900756836</v>
+        <v>33.36514282226562</v>
       </c>
       <c r="C62" t="n">
         <v>33.68000030517578</v>
@@ -1683,7 +1695,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1708,11 +1720,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>44.51987838745117</v>
+        <v>44.51988220214844</v>
       </c>
       <c r="C64" t="n">
         <v>44.93999862670898</v>
@@ -1733,11 +1745,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>50.56285858154297</v>
+        <v>50.56285095214844</v>
       </c>
       <c r="C65" t="n">
         <v>51.04000091552734</v>
@@ -1758,11 +1770,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>59.45890045166016</v>
+        <v>59.45890426635742</v>
       </c>
       <c r="C66" t="n">
         <v>60.02000045776367</v>
@@ -1783,11 +1795,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>56.17984771728516</v>
+        <v>56.17984390258789</v>
       </c>
       <c r="C67" t="n">
         <v>56.70999908447266</v>
@@ -1808,7 +1820,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1833,7 +1845,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
@@ -1858,11 +1870,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>57.65591812133789</v>
+        <v>57.65592193603516</v>
       </c>
       <c r="C70" t="n">
         <v>58.20000076293945</v>
@@ -1883,11 +1895,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>54.78302764892578</v>
+        <v>54.78302383422852</v>
       </c>
       <c r="C71" t="n">
         <v>55.29999923706055</v>
@@ -1908,11 +1920,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>58.86450576782227</v>
+        <v>58.86450958251953</v>
       </c>
       <c r="C72" t="n">
         <v>59.41999816894531</v>
@@ -1933,11 +1945,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>54.91180801391602</v>
+        <v>54.91181182861328</v>
       </c>
       <c r="C73" t="n">
         <v>55.43000030517578</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>90.01059722900391</v>
+        <v>90.01058959960938</v>
       </c>
       <c r="C74" t="n">
         <v>90.86000061035156</v>
@@ -1983,7 +1995,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2010,7 +2022,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2037,11 +2049,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>133.9955291748047</v>
+        <v>133.9955139160156</v>
       </c>
       <c r="C77" t="n">
         <v>135.2599945068359</v>
@@ -2064,11 +2076,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>134.3818511962891</v>
+        <v>134.3818969726562</v>
       </c>
       <c r="C78" t="n">
         <v>135.6499938964844</v>
@@ -2091,11 +2103,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>113.152214050293</v>
+        <v>113.1522216796875</v>
       </c>
       <c r="C79" t="n">
         <v>114.2200012207031</v>
@@ -2118,11 +2130,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>133.3912048339844</v>
+        <v>133.3912200927734</v>
       </c>
       <c r="C80" t="n">
         <v>134.6499938964844</v>
@@ -2145,11 +2157,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>146.6659698486328</v>
+        <v>146.6659393310547</v>
       </c>
       <c r="C81" t="n">
         <v>148.0500030517578</v>
@@ -2172,11 +2184,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>151.2328643798828</v>
+        <v>151.2328338623047</v>
       </c>
       <c r="C82" t="n">
         <v>152.6600036621094</v>
@@ -2199,11 +2211,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>140.9697113037109</v>
+        <v>140.9697265625</v>
       </c>
       <c r="C83" t="n">
         <v>142.3000030517578</v>
@@ -2226,11 +2238,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>174.8995208740234</v>
+        <v>174.8995056152344</v>
       </c>
       <c r="C84" t="n">
         <v>176.5500030517578</v>
@@ -2253,7 +2265,7 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
@@ -2280,11 +2292,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>172.3139190673828</v>
+        <v>172.3139038085938</v>
       </c>
       <c r="C86" t="n">
         <v>173.9400024414062</v>
@@ -2307,11 +2319,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>165.4388122558594</v>
+        <v>165.4387817382812</v>
       </c>
       <c r="C87" t="n">
         <v>167</v>
@@ -2336,11 +2348,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>174.7509460449219</v>
+        <v>174.7509307861328</v>
       </c>
       <c r="C88" t="n">
         <v>176.3999938964844</v>
@@ -2365,11 +2377,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>213.1287536621094</v>
+        <v>213.1287689208984</v>
       </c>
       <c r="C89" t="n">
         <v>215.1399993896484</v>
@@ -2394,7 +2406,7 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
@@ -2423,11 +2435,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>222.7777252197266</v>
+        <v>222.7776947021484</v>
       </c>
       <c r="C91" t="n">
         <v>224.8800048828125</v>
@@ -2452,7 +2464,7 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
@@ -2481,7 +2493,7 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
@@ -2510,7 +2522,7 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
@@ -2539,11 +2551,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>284.911376953125</v>
+        <v>284.9114074707031</v>
       </c>
       <c r="C95" t="n">
         <v>287.6000061035156</v>
@@ -2568,11 +2580,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>291.1128540039062</v>
+        <v>291.1128234863281</v>
       </c>
       <c r="C96" t="n">
         <v>293.8599853515625</v>
@@ -2597,11 +2609,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>272.6669311523438</v>
+        <v>272.6669006347656</v>
       </c>
       <c r="C97" t="n">
         <v>275.239990234375</v>
@@ -2626,11 +2638,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>285.89208984375</v>
+        <v>285.8921203613281</v>
       </c>
       <c r="C98" t="n">
         <v>288.5899963378906</v>
@@ -2655,11 +2667,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>329.3916320800781</v>
+        <v>329.3916015625</v>
       </c>
       <c r="C99" t="n">
         <v>332.5</v>
@@ -2684,11 +2696,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>297.4728088378906</v>
+        <v>297.4728698730469</v>
       </c>
       <c r="C100" t="n">
         <v>300.2799987792969</v>
@@ -2713,11 +2725,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>294.1145629882812</v>
+        <v>294.1145324707031</v>
       </c>
       <c r="C101" t="n">
         <v>296.8900146484375</v>
@@ -2742,11 +2754,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>304.09033203125</v>
+        <v>304.0903625488281</v>
       </c>
       <c r="C102" t="n">
         <v>306.9599914550781</v>
@@ -2771,7 +2783,7 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
@@ -2800,7 +2812,7 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
@@ -2829,11 +2841,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>347.1837158203125</v>
+        <v>347.1836853027344</v>
       </c>
       <c r="C105" t="n">
         <v>350.4599914550781</v>
@@ -2858,11 +2870,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>357.149658203125</v>
+        <v>357.1496887207031</v>
       </c>
       <c r="C106" t="n">
         <v>360.5199890136719</v>
@@ -2887,7 +2899,7 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
@@ -2916,11 +2928,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>412.219970703125</v>
+        <v>412.2200012207031</v>
       </c>
       <c r="C108" t="n">
         <v>416.1099853515625</v>
@@ -2945,11 +2957,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>406.414794921875</v>
+        <v>406.4147644042969</v>
       </c>
       <c r="C109" t="n">
         <v>410.25</v>
@@ -2974,11 +2986,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>412.7648620605469</v>
+        <v>412.764892578125</v>
       </c>
       <c r="C110" t="n">
         <v>416.6600036621094</v>
@@ -3003,7 +3015,7 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
@@ -3032,7 +3044,7 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
@@ -3061,11 +3073,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>453.1834411621094</v>
+        <v>453.1834106445312</v>
       </c>
       <c r="C113" t="n">
         <v>457.4599914550781</v>
@@ -3090,11 +3102,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>507.7682800292969</v>
+        <v>507.7683410644531</v>
       </c>
       <c r="C114" t="n">
         <v>512.5599975585938</v>
@@ -3119,11 +3131,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>505.3610534667969</v>
+        <v>505.361083984375</v>
       </c>
       <c r="C115" t="n">
         <v>510.1300048828125</v>
@@ -3148,7 +3160,7 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
@@ -3177,11 +3189,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>508.6994934082031</v>
+        <v>508.6995544433594</v>
       </c>
       <c r="C117" t="n">
         <v>513.5</v>
@@ -3206,11 +3218,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>460.7916564941406</v>
+        <v>460.7916259765625</v>
       </c>
       <c r="C118" t="n">
         <v>465.1400146484375</v>
@@ -3235,7 +3247,7 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
@@ -3264,11 +3276,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>539.4097900390625</v>
+        <v>539.40966796875</v>
       </c>
       <c r="C120" t="n">
         <v>544.5</v>
@@ -3293,11 +3305,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>537.7949829101562</v>
+        <v>537.794921875</v>
       </c>
       <c r="C121" t="n">
         <v>542.8699951171875</v>
@@ -3322,11 +3334,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>416.1627502441406</v>
+        <v>416.1628112792969</v>
       </c>
       <c r="C122" t="n">
         <v>420.0899963378906</v>
@@ -3351,7 +3363,7 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
@@ -3380,11 +3392,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>357.0703735351562</v>
+        <v>357.0704040527344</v>
       </c>
       <c r="C124" t="n">
         <v>360.4400024414062</v>
@@ -3409,11 +3421,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>373.1883544921875</v>
+        <v>373.1883239746094</v>
       </c>
       <c r="C125" t="n">
         <v>376.7099914550781</v>
@@ -3438,11 +3450,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>395.2005310058594</v>
+        <v>395.2005920410156</v>
       </c>
       <c r="C126" t="n">
         <v>398.9299926757812</v>
@@ -3467,7 +3479,7 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
@@ -3496,11 +3508,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>421.1457824707031</v>
+        <v>421.145751953125</v>
       </c>
       <c r="C128" t="n">
         <v>425.1199951171875</v>
@@ -3525,7 +3537,7 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
@@ -3554,11 +3566,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>398.2616882324219</v>
+        <v>398.26171875</v>
       </c>
       <c r="C130" t="n">
         <v>402.0199890136719</v>
@@ -3583,11 +3595,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>341.7945861816406</v>
+        <v>341.7945556640625</v>
       </c>
       <c r="C131" t="n">
         <v>345.0199890136719</v>
@@ -3612,11 +3624,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>375.6946716308594</v>
+        <v>375.6947021484375</v>
       </c>
       <c r="C132" t="n">
         <v>379.239990234375</v>
@@ -3641,7 +3653,7 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
@@ -3670,11 +3682,11 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>355.93115234375</v>
+        <v>355.9311828613281</v>
       </c>
       <c r="C134" t="n">
         <v>359.2900085449219</v>
@@ -3699,7 +3711,7 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
@@ -3728,7 +3740,7 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
@@ -3757,11 +3769,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>384.8581848144531</v>
+        <v>384.8582458496094</v>
       </c>
       <c r="C137" t="n">
         <v>388.489990234375</v>
@@ -3786,11 +3798,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>454.7684936523438</v>
+        <v>454.7684326171875</v>
       </c>
       <c r="C138" t="n">
         <v>459.0599975585938</v>
@@ -3815,7 +3827,7 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
@@ -3844,7 +3856,7 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
@@ -3873,11 +3885,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>492.2546997070312</v>
+        <v>492.2547302246094</v>
       </c>
       <c r="C141" t="n">
         <v>496.8999938964844</v>
@@ -3902,11 +3914,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>442.9400939941406</v>
+        <v>442.9401245117188</v>
       </c>
       <c r="C142" t="n">
         <v>447.1199951171875</v>
@@ -3931,11 +3943,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>398.8561096191406</v>
+        <v>398.8560485839844</v>
       </c>
       <c r="C143" t="n">
         <v>402.6199951171875</v>
@@ -3960,11 +3972,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>358.4770812988281</v>
+        <v>358.4771118164062</v>
       </c>
       <c r="C144" t="n">
         <v>361.8599853515625</v>
@@ -3989,11 +4001,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>372.4453430175781</v>
+        <v>372.4453125</v>
       </c>
       <c r="C145" t="n">
         <v>375.9599914550781</v>
@@ -4018,7 +4030,7 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
@@ -4047,7 +4059,7 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
@@ -4076,7 +4088,7 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
@@ -4105,7 +4117,7 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
@@ -4134,11 +4146,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>297.512451171875</v>
+        <v>297.5124816894531</v>
       </c>
       <c r="C150" t="n">
         <v>300.3200073242188</v>
@@ -4163,11 +4175,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>341.7648315429688</v>
+        <v>341.7648620605469</v>
       </c>
       <c r="C151" t="n">
         <v>344.989990234375</v>
@@ -4192,11 +4204,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>364.5696411132812</v>
+        <v>364.5696716308594</v>
       </c>
       <c r="C152" t="n">
         <v>368.010009765625</v>
@@ -4221,11 +4233,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>402.947509765625</v>
+        <v>402.9475402832031</v>
       </c>
       <c r="C153" t="n">
         <v>406.75</v>
@@ -4250,11 +4262,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>400.2628784179688</v>
+        <v>400.2628173828125</v>
       </c>
       <c r="C154" t="n">
         <v>404.0400085449219</v>
@@ -4279,11 +4291,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>336.0686340332031</v>
+        <v>336.0685729980469</v>
       </c>
       <c r="C155" t="n">
         <v>339.239990234375</v>
@@ -4308,11 +4320,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>362.2317199707031</v>
+        <v>362.231689453125</v>
       </c>
       <c r="C156" t="n">
         <v>365.6499938964844</v>
@@ -4337,7 +4349,7 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
@@ -4366,11 +4378,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>425.2569580078125</v>
+        <v>425.2569274902344</v>
       </c>
       <c r="C158" t="n">
         <v>429.2699890136719</v>
@@ -4395,11 +4407,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>426.7132263183594</v>
+        <v>426.7131652832031</v>
       </c>
       <c r="C159" t="n">
         <v>430.739990234375</v>
@@ -4424,11 +4436,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>406.7813110351562</v>
+        <v>406.7812805175781</v>
       </c>
       <c r="C160" t="n">
         <v>410.6199951171875</v>
@@ -4453,11 +4465,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>339.9321899414062</v>
+        <v>339.93212890625</v>
       </c>
       <c r="C161" t="n">
         <v>343.1400146484375</v>
@@ -4482,7 +4494,7 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
@@ -4511,11 +4523,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>310.0739440917969</v>
+        <v>310.0739135742188</v>
       </c>
       <c r="C163" t="n">
         <v>313</v>
@@ -4540,11 +4552,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>301.9109497070312</v>
+        <v>301.9109802246094</v>
       </c>
       <c r="C164" t="n">
         <v>304.760009765625</v>
@@ -4569,11 +4581,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>287.3384094238281</v>
+        <v>287.3384399414062</v>
       </c>
       <c r="C165" t="n">
         <v>290.0499877929688</v>
@@ -4598,11 +4610,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>274.8066711425781</v>
+        <v>274.8067321777344</v>
       </c>
       <c r="C166" t="n">
         <v>277.3999938964844</v>
@@ -4627,7 +4639,7 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
@@ -4656,11 +4668,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>365.5504150390625</v>
+        <v>365.5503845214844</v>
       </c>
       <c r="C168" t="n">
         <v>369</v>
@@ -4685,7 +4697,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4714,11 +4726,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>334.78076171875</v>
+        <v>334.7807312011719</v>
       </c>
       <c r="C170" t="n">
         <v>337.9400024414062</v>
@@ -4743,7 +4755,7 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
@@ -4772,11 +4784,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>483.7252197265625</v>
+        <v>483.7252502441406</v>
       </c>
       <c r="C172" t="n">
         <v>488.2900085449219</v>
@@ -4801,11 +4813,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>520.9637451171875</v>
+        <v>520.9638061523438</v>
       </c>
       <c r="C173" t="n">
         <v>525.8800048828125</v>
@@ -4830,11 +4842,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>607.0811767578125</v>
+        <v>607.0811157226562</v>
       </c>
       <c r="C174" t="n">
         <v>612.8099975585938</v>
@@ -4859,7 +4871,7 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
@@ -4888,11 +4900,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>626.1610107421875</v>
+        <v>626.1611938476562</v>
       </c>
       <c r="C176" t="n">
         <v>632.0700073242188</v>
@@ -4917,11 +4929,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>614.134521484375</v>
+        <v>614.1345825195312</v>
       </c>
       <c r="C177" t="n">
         <v>619.9299926757812</v>
@@ -4946,11 +4958,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>554.5469360351562</v>
+        <v>554.5469970703125</v>
       </c>
       <c r="C178" t="n">
         <v>559.780029296875</v>
@@ -4975,7 +4987,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5004,11 +5016,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>511.2059326171875</v>
+        <v>511.2059631347656</v>
       </c>
       <c r="C180" t="n">
         <v>516.030029296875</v>
@@ -5033,11 +5045,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>478.5935974121094</v>
+        <v>478.5936584472656</v>
       </c>
       <c r="C181" t="n">
         <v>483.1099853515625</v>
@@ -5062,11 +5074,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>499.1298828125</v>
+        <v>499.1298522949219</v>
       </c>
       <c r="C182" t="n">
         <v>503.8399963378906</v>
@@ -5091,7 +5103,7 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
@@ -5120,11 +5132,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>468.7168273925781</v>
+        <v>468.7168579101562</v>
       </c>
       <c r="C184" t="n">
         <v>473.1400146484375</v>
@@ -5149,11 +5161,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>476.8005676269531</v>
+        <v>476.800537109375</v>
       </c>
       <c r="C185" t="n">
         <v>481.2999877929688</v>
@@ -5178,7 +5190,7 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
@@ -5207,11 +5219,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>553.318359375</v>
+        <v>553.3184814453125</v>
       </c>
       <c r="C187" t="n">
         <v>558.5399780273438</v>
@@ -5236,11 +5248,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>569.2383422851562</v>
+        <v>569.23828125</v>
       </c>
       <c r="C188" t="n">
         <v>574.6099853515625</v>
@@ -5265,11 +5277,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>667.1046752929688</v>
+        <v>667.104736328125</v>
       </c>
       <c r="C189" t="n">
         <v>673.4000244140625</v>
@@ -5294,7 +5306,7 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
@@ -5323,11 +5335,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>633.9575805664062</v>
+        <v>633.9574584960938</v>
       </c>
       <c r="C191" t="n">
         <v>639.9400024414062</v>
@@ -5352,11 +5364,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>630.5794677734375</v>
+        <v>630.5794067382812</v>
       </c>
       <c r="C192" t="n">
         <v>636.530029296875</v>
@@ -5381,7 +5393,7 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
@@ -5410,11 +5422,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>602.9005737304688</v>
+        <v>602.900634765625</v>
       </c>
       <c r="C194" t="n">
         <v>608.5900268554688</v>
@@ -5439,11 +5451,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>612.5792236328125</v>
+        <v>612.5792846679688</v>
       </c>
       <c r="C195" t="n">
         <v>618.3599853515625</v>
@@ -5468,11 +5480,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>691.8908081054688</v>
+        <v>691.890869140625</v>
       </c>
       <c r="C196" t="n">
         <v>698.4199829101562</v>
@@ -5497,11 +5509,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>652.9483642578125</v>
+        <v>652.9483032226562</v>
       </c>
       <c r="C197" t="n">
         <v>659.1099853515625</v>
@@ -5526,11 +5538,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>658.5256958007812</v>
+        <v>658.525634765625</v>
       </c>
       <c r="C198" t="n">
         <v>664.739990234375</v>
@@ -5555,11 +5567,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>585.603759765625</v>
+        <v>585.6038208007812</v>
       </c>
       <c r="C199" t="n">
         <v>591.1300048828125</v>
@@ -5584,11 +5596,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>576.2520751953125</v>
+        <v>576.2521362304688</v>
       </c>
       <c r="C200" t="n">
         <v>581.6900024414062</v>
@@ -5613,11 +5625,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>575.6279296875</v>
+        <v>575.6279907226562</v>
       </c>
       <c r="C201" t="n">
         <v>581.0599975585938</v>
@@ -5642,11 +5654,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>682.4300537109375</v>
+        <v>682.4301147460938</v>
       </c>
       <c r="C202" t="n">
         <v>688.8699951171875</v>
@@ -5671,7 +5683,7 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
@@ -5700,11 +5712,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>744.6727294921875</v>
+        <v>744.6727905273438</v>
       </c>
       <c r="C204" t="n">
         <v>751.7000122070312</v>
@@ -5729,11 +5741,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>714.7451171875</v>
+        <v>714.7451782226562</v>
       </c>
       <c r="C205" t="n">
         <v>721.489990234375</v>
@@ -5758,11 +5770,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>751.3794555664062</v>
+        <v>751.37939453125</v>
       </c>
       <c r="C206" t="n">
         <v>758.469970703125</v>
@@ -5787,7 +5799,7 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
@@ -5816,11 +5828,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>813.9885864257812</v>
+        <v>813.9886474609375</v>
       </c>
       <c r="C208" t="n">
         <v>821.6699829101562</v>
@@ -5845,11 +5857,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>794.2944946289062</v>
+        <v>794.29443359375</v>
       </c>
       <c r="C209" t="n">
         <v>801.7899780273438</v>
@@ -5874,11 +5886,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>728.6835327148438</v>
+        <v>728.6836547851562</v>
       </c>
       <c r="C210" t="n">
         <v>735.5599975585938</v>
@@ -5903,11 +5915,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>711.8226928710938</v>
+        <v>711.82275390625</v>
       </c>
       <c r="C211" t="n">
         <v>718.5399780273438</v>
@@ -5932,11 +5944,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>734.9742431640625</v>
+        <v>734.9741821289062</v>
       </c>
       <c r="C212" t="n">
         <v>741.9099731445312</v>
@@ -5961,11 +5973,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>818.7635498046875</v>
+        <v>818.7634887695312</v>
       </c>
       <c r="C213" t="n">
         <v>826.489990234375</v>
@@ -5990,11 +6002,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>815.2665405273438</v>
+        <v>815.2664794921875</v>
       </c>
       <c r="C214" t="n">
         <v>822.9600219726562</v>
@@ -6019,7 +6031,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6048,7 +6060,7 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
@@ -6077,7 +6089,7 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
@@ -6106,7 +6118,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6135,11 +6147,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>957.05859375</v>
+        <v>957.0585327148438</v>
       </c>
       <c r="C219" t="n">
         <v>966.0900268554688</v>
@@ -6164,7 +6176,7 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
@@ -6193,11 +6205,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>882.3335571289062</v>
+        <v>882.3336181640625</v>
       </c>
       <c r="C221" t="n">
         <v>890.6599731445312</v>
@@ -6222,11 +6234,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>970.9969482421875</v>
+        <v>970.9968872070312</v>
       </c>
       <c r="C222" t="n">
         <v>980.1599731445312</v>
@@ -6251,11 +6263,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>1041.204345703125</v>
+        <v>1041.204467773438</v>
       </c>
       <c r="C223" t="n">
         <v>1051.030029296875</v>
@@ -6280,11 +6292,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>1069.10107421875</v>
+        <v>1069.100952148438</v>
       </c>
       <c r="C224" t="n">
         <v>1079.18994140625</v>
@@ -6309,7 +6321,7 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
@@ -6338,11 +6350,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>1041.412475585938</v>
+        <v>1041.41259765625</v>
       </c>
       <c r="C226" t="n">
         <v>1051.239990234375</v>
@@ -6367,7 +6379,7 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
@@ -6396,7 +6408,7 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
@@ -6425,11 +6437,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>705.6707153320312</v>
+        <v>705.6707763671875</v>
       </c>
       <c r="C229" t="n">
         <v>712.3300170898438</v>
@@ -6454,11 +6466,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>666.6885986328125</v>
+        <v>666.6886596679688</v>
       </c>
       <c r="C230" t="n">
         <v>672.97998046875</v>
@@ -6483,11 +6495,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>693.097412109375</v>
+        <v>693.0973510742188</v>
       </c>
       <c r="C231" t="n">
         <v>698.739990234375</v>
@@ -6512,7 +6524,7 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
@@ -6541,7 +6553,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6570,7 +6582,7 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
@@ -6599,7 +6611,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6628,7 +6640,7 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
@@ -6657,11 +6669,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>577.7374877929688</v>
+        <v>577.737548828125</v>
       </c>
       <c r="C237" t="n">
         <v>580.7000122070312</v>
@@ -6686,11 +6698,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>559.4015502929688</v>
+        <v>559.4014892578125</v>
       </c>
       <c r="C238" t="n">
         <v>562.27001953125</v>
@@ -6715,7 +6727,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6744,7 +6756,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6773,7 +6785,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6802,7 +6814,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6831,7 +6843,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -6860,7 +6872,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -6889,7 +6901,7 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
@@ -6918,7 +6930,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -6947,7 +6959,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -6976,7 +6988,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7005,7 +7017,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7034,32 +7046,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>801.8200073242188</v>
+        <v>796.02001953125</v>
       </c>
       <c r="C250" t="n">
-        <v>801.8200073242188</v>
+        <v>796.02001953125</v>
       </c>
       <c r="D250" t="n">
-        <v>11353800</v>
+        <v>11956400</v>
       </c>
       <c r="E250" t="n">
         <v>40.38</v>
       </c>
       <c r="F250" t="n">
-        <v>19.85686001298214</v>
+        <v>19.71322485218549</v>
       </c>
       <c r="G250" t="n">
         <v>102800000</v>
       </c>
       <c r="H250" t="n">
-        <v>82427096752.92969</v>
+        <v>81830858007.8125</v>
       </c>
       <c r="I250" t="n">
-        <v>0.1104455252918288</v>
+        <v>0.116307392996109</v>
       </c>
     </row>
   </sheetData>
@@ -7091,75 +7103,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7195,13 +7207,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7237,13 +7249,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7279,13 +7291,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7312,7 +7324,7 @@
       <c r="I5" t="n">
         <v>-1.27</v>
       </c>
-      <c r="J5" s="1" t="n">
+      <c r="J5" s="2" t="n">
         <v>40960</v>
       </c>
       <c r="K5" t="n">
@@ -7325,13 +7337,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7358,7 +7370,7 @@
       <c r="I6" t="n">
         <v>-1.38</v>
       </c>
-      <c r="J6" s="1" t="n">
+      <c r="J6" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="K6" t="n">
@@ -7371,13 +7383,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7404,7 +7416,7 @@
       <c r="I7" t="n">
         <v>-1.76</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="K7" t="n">
@@ -7417,13 +7429,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7450,7 +7462,7 @@
       <c r="I8" t="n">
         <v>-2.03</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="K8" t="n">
@@ -7463,13 +7475,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7496,7 +7508,7 @@
       <c r="I9" t="n">
         <v>-2.45</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K9" t="n">
@@ -7509,13 +7521,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7542,7 +7554,7 @@
       <c r="I10" t="n">
         <v>-1.85</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K10" t="n">
@@ -7555,13 +7567,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7588,7 +7600,7 @@
       <c r="I11" t="n">
         <v>-0.4600000000000003</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K11" t="n">
@@ -7601,13 +7613,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7634,7 +7646,7 @@
       <c r="I12" t="n">
         <v>1.94</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K12" t="n">
@@ -7647,13 +7659,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7680,7 +7692,7 @@
       <c r="I13" t="n">
         <v>6.609999999999999</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="K13" t="n">
@@ -7693,13 +7705,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7726,7 +7738,7 @@
       <c r="I14" t="n">
         <v>7.399999999999999</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="K14" t="n">
@@ -7739,13 +7751,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7772,7 +7784,7 @@
       <c r="I15" t="n">
         <v>7.49</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="K15" t="n">
@@ -7785,13 +7797,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7818,7 +7830,7 @@
       <c r="I16" t="n">
         <v>7.02</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="K16" t="n">
@@ -7831,13 +7843,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -7864,7 +7876,7 @@
       <c r="I17" t="n">
         <v>3.799999999999999</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="K17" t="n">
@@ -7877,13 +7889,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -7910,7 +7922,7 @@
       <c r="I18" t="n">
         <v>3.479999999999999</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="K18" t="n">
@@ -7923,13 +7935,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -7956,7 +7968,7 @@
       <c r="I19" t="n">
         <v>3.509999999999999</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="K19" t="n">
@@ -7969,13 +7981,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8002,7 +8014,7 @@
       <c r="I20" t="n">
         <v>2.959999999999999</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="K20" t="n">
@@ -8015,13 +8027,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8048,7 +8060,7 @@
       <c r="I21" t="n">
         <v>3.059999999999999</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="K21" t="n">
@@ -8061,13 +8073,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8094,7 +8106,7 @@
       <c r="I22" t="n">
         <v>3.139999999999999</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="K22" t="n">
@@ -8107,13 +8119,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8140,7 +8152,7 @@
       <c r="I23" t="n">
         <v>4.009999999999999</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="K23" t="n">
@@ -8153,13 +8165,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8186,7 +8198,7 @@
       <c r="I24" t="n">
         <v>5.129999999999999</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="K24" t="n">
@@ -8199,13 +8211,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8232,7 +8244,7 @@
       <c r="I25" t="n">
         <v>5.509999999999999</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="K25" t="n">
@@ -8245,13 +8257,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8278,7 +8290,7 @@
       <c r="I26" t="n">
         <v>6.299999999999999</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="K26" t="n">
@@ -8291,13 +8303,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8324,7 +8336,7 @@
       <c r="I27" t="n">
         <v>6.299999999999999</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="K27" t="n">
@@ -8337,13 +8349,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8370,7 +8382,7 @@
       <c r="I28" t="n">
         <v>6.749999999999999</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="K28" t="n">
@@ -8383,13 +8395,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8416,7 +8428,7 @@
       <c r="I29" t="n">
         <v>7.6</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="K29" t="n">
@@ -8429,13 +8441,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8462,7 +8474,7 @@
       <c r="I30" t="n">
         <v>8.309999999999999</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="K30" t="n">
@@ -8475,13 +8487,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8508,7 +8520,7 @@
       <c r="I31" t="n">
         <v>9.959999999999999</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="K31" t="n">
@@ -8521,13 +8533,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>43047</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8554,7 +8566,7 @@
       <c r="I32" t="n">
         <v>11.01</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>43047</v>
       </c>
       <c r="K32" t="n">
@@ -8567,13 +8579,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8600,7 +8612,7 @@
       <c r="I33" t="n">
         <v>10.32</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="K33" t="n">
@@ -8613,13 +8625,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8646,7 +8658,7 @@
       <c r="I34" t="n">
         <v>12.32</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="K34" t="n">
@@ -8659,13 +8671,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8692,7 +8704,7 @@
       <c r="I35" t="n">
         <v>13.8</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="K35" t="n">
@@ -8705,13 +8717,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8738,7 +8750,7 @@
       <c r="I36" t="n">
         <v>15.65</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="K36" t="n">
@@ -8751,13 +8763,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8784,7 +8796,7 @@
       <c r="I37" t="n">
         <v>21.3</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="K37" t="n">
@@ -8797,13 +8809,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8830,7 +8842,7 @@
       <c r="I38" t="n">
         <v>21.13</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="K38" t="n">
@@ -8843,13 +8855,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -8876,7 +8888,7 @@
       <c r="I39" t="n">
         <v>17.99</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="K39" t="n">
@@ -8889,13 +8901,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -8922,7 +8934,7 @@
       <c r="I40" t="n">
         <v>18.68</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="K40" t="n">
@@ -8935,13 +8947,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -8968,7 +8980,7 @@
       <c r="I41" t="n">
         <v>18.46</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="K41" t="n">
@@ -8981,13 +8993,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9014,7 +9026,7 @@
       <c r="I42" t="n">
         <v>19.9</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="K42" t="n">
@@ -9027,13 +9039,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9060,7 +9072,7 @@
       <c r="I43" t="n">
         <v>25.83</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="K43" t="n">
@@ -9073,13 +9085,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9106,7 +9118,7 @@
       <c r="I44" t="n">
         <v>27.36</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="K44" t="n">
@@ -9119,13 +9131,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9152,7 +9164,7 @@
       <c r="I45" t="n">
         <v>30.67</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="K45" t="n">
@@ -9165,13 +9177,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9198,7 +9210,7 @@
       <c r="I46" t="n">
         <v>35.33</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="K46" t="n">
@@ -9211,13 +9223,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9244,7 +9256,7 @@
       <c r="I47" t="n">
         <v>55.69</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="K47" t="n">
@@ -9257,13 +9269,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9290,7 +9302,7 @@
       <c r="I48" t="n">
         <v>62.63</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="K48" t="n">
@@ -9303,13 +9315,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9336,7 +9348,7 @@
       <c r="I49" t="n">
         <v>71.97</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="K49" t="n">
@@ -9349,13 +9361,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9382,7 +9394,7 @@
       <c r="I50" t="n">
         <v>70.48999999999998</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="K50" t="n">
@@ -9395,13 +9407,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9428,7 +9440,7 @@
       <c r="I51" t="n">
         <v>49.98999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="K51" t="n">
@@ -9441,13 +9453,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9474,7 +9486,7 @@
       <c r="I52" t="n">
         <v>47.31999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="K52" t="n">
@@ -9487,13 +9499,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9520,7 +9532,7 @@
       <c r="I53" t="n">
         <v>38.21999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="K53" t="n">
@@ -9533,13 +9545,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9566,7 +9578,7 @@
       <c r="I54" t="n">
         <v>36.77999999999999</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="K54" t="n">
@@ -9579,13 +9591,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9612,7 +9624,7 @@
       <c r="I55" t="n">
         <v>37.81</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="K55" t="n">
@@ -9625,13 +9637,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9658,7 +9670,7 @@
       <c r="I56" t="n">
         <v>35.03999999999999</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="K56" t="n">
@@ -9671,13 +9683,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9704,7 +9716,7 @@
       <c r="I57" t="n">
         <v>34.77</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="K57" t="n">
@@ -9717,13 +9729,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9750,7 +9762,7 @@
       <c r="I58" t="n">
         <v>33.86999999999999</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="K58" t="n">
@@ -9763,13 +9775,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9796,7 +9808,7 @@
       <c r="I59" t="n">
         <v>37.77999999999999</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="K59" t="n">
@@ -9809,13 +9821,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9842,7 +9854,7 @@
       <c r="I60" t="n">
         <v>40.42999999999999</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="K60" t="n">
@@ -9855,13 +9867,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -9888,7 +9900,7 @@
       <c r="I61" t="n">
         <v>38.34</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="K61" t="n">
@@ -9901,13 +9913,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -9934,7 +9946,7 @@
       <c r="I62" t="n">
         <v>39.34</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="K62" t="n">
@@ -9947,13 +9959,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -9980,7 +9992,7 @@
       <c r="I63" t="n">
         <v>39.73999999999999</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="K63" t="n">
@@ -9993,13 +10005,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10026,7 +10038,7 @@
       <c r="I64" t="n">
         <v>41.81999999999999</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="K64" t="n">
@@ -10039,13 +10051,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10072,7 +10084,7 @@
       <c r="I65" t="n">
         <v>41.47999999999999</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="K65" t="n">
@@ -10085,13 +10097,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10118,7 +10130,7 @@
       <c r="I66" t="n">
         <v>40.95999999999999</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="K66" t="n">
@@ -10131,13 +10143,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10164,7 +10176,7 @@
       <c r="I67" t="n">
         <v>40.38</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="K67" t="n">
@@ -10202,57 +10214,57 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40374</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40387</v>
       </c>
       <c r="C2" t="n">
@@ -10282,10 +10294,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40479</v>
       </c>
       <c r="C3" t="n">
@@ -10315,10 +10327,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40585</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40591</v>
       </c>
       <c r="C4" t="n">
@@ -10348,10 +10360,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40646</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40666</v>
       </c>
       <c r="C5" t="n">
@@ -10381,10 +10393,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40752</v>
       </c>
       <c r="C6" t="n">
@@ -10414,10 +10426,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40835</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40843</v>
       </c>
       <c r="C7" t="n">
@@ -10447,10 +10459,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C8" t="n">
@@ -10484,10 +10496,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>41025</v>
       </c>
       <c r="C9" t="n">
@@ -10521,10 +10533,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C10" t="n">
@@ -10558,10 +10570,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>41115</v>
       </c>
       <c r="C11" t="n">
@@ -10595,10 +10607,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C12" t="n">
@@ -10632,10 +10644,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41206</v>
       </c>
       <c r="C13" t="n">
@@ -10669,10 +10681,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="C14" t="n">
@@ -10706,10 +10718,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="C15" t="n">
@@ -10743,10 +10755,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41320</v>
       </c>
       <c r="C16" t="n">
@@ -10780,10 +10792,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41397</v>
       </c>
       <c r="C17" t="n">
@@ -10817,10 +10829,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41492</v>
       </c>
       <c r="C18" t="n">
@@ -10854,10 +10866,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41583</v>
       </c>
       <c r="C19" t="n">
@@ -10891,10 +10903,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41683</v>
       </c>
       <c r="C20" t="n">
@@ -10928,10 +10940,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41767</v>
       </c>
       <c r="C21" t="n">
@@ -10965,10 +10977,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41856</v>
       </c>
       <c r="C22" t="n">
@@ -11002,10 +11014,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41947</v>
       </c>
       <c r="C23" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42047</v>
       </c>
       <c r="C24" t="n">
@@ -11076,10 +11088,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42131</v>
       </c>
       <c r="C25" t="n">
@@ -11113,10 +11125,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42220</v>
       </c>
       <c r="C26" t="n">
@@ -11150,10 +11162,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42312</v>
       </c>
       <c r="C27" t="n">
@@ -11187,10 +11199,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42411</v>
       </c>
       <c r="C28" t="n">
@@ -11224,10 +11236,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42495</v>
       </c>
       <c r="C29" t="n">
@@ -11261,10 +11273,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42586</v>
       </c>
       <c r="C30" t="n">
@@ -11298,10 +11310,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42678</v>
       </c>
       <c r="C31" t="n">
@@ -11335,10 +11347,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42775</v>
       </c>
       <c r="C32" t="n">
@@ -11372,10 +11384,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42859</v>
       </c>
       <c r="C33" t="n">
@@ -11409,10 +11421,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42950</v>
       </c>
       <c r="C34" t="n">
@@ -11446,10 +11458,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43047</v>
       </c>
       <c r="C35" t="n">
@@ -11483,10 +11495,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43139</v>
       </c>
       <c r="C36" t="n">
@@ -11520,10 +11532,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43223</v>
       </c>
       <c r="C37" t="n">
@@ -11557,10 +11569,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43314</v>
       </c>
       <c r="C38" t="n">
@@ -11594,10 +11606,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43410</v>
       </c>
       <c r="C39" t="n">
@@ -11631,10 +11643,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43503</v>
       </c>
       <c r="C40" t="n">
@@ -11668,10 +11680,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43592</v>
       </c>
       <c r="C41" t="n">
@@ -11705,10 +11717,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43683</v>
       </c>
       <c r="C42" t="n">
@@ -11742,10 +11754,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43774</v>
       </c>
       <c r="C43" t="n">
@@ -11779,10 +11791,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="C44" t="n">
@@ -11816,10 +11828,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43956</v>
       </c>
       <c r="C45" t="n">
@@ -11853,10 +11865,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44048</v>
       </c>
       <c r="C46" t="n">
@@ -11890,10 +11902,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44140</v>
       </c>
       <c r="C47" t="n">
@@ -11927,10 +11939,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44235</v>
       </c>
       <c r="C48" t="n">
@@ -11964,10 +11976,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44322</v>
       </c>
       <c r="C49" t="n">
@@ -12001,10 +12013,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44413</v>
       </c>
       <c r="C50" t="n">
@@ -12038,10 +12050,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44504</v>
       </c>
       <c r="C51" t="n">
@@ -12075,10 +12087,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44599</v>
       </c>
       <c r="C52" t="n">
@@ -12112,10 +12124,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44685</v>
       </c>
       <c r="C53" t="n">
@@ -12149,10 +12161,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44776</v>
       </c>
       <c r="C54" t="n">
@@ -12186,10 +12198,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44868</v>
       </c>
       <c r="C55" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44963</v>
       </c>
       <c r="C56" t="n">
@@ -12260,10 +12272,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45050</v>
       </c>
       <c r="C57" t="n">
@@ -12297,10 +12309,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45141</v>
       </c>
       <c r="C58" t="n">
@@ -12334,10 +12346,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45232</v>
       </c>
       <c r="C59" t="n">
@@ -12371,10 +12383,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45327</v>
       </c>
       <c r="C60" t="n">
@@ -12408,10 +12420,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45414</v>
       </c>
       <c r="C61" t="n">
@@ -12445,10 +12457,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45505</v>
       </c>
       <c r="C62" t="n">
@@ -12482,10 +12494,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="C63" t="n">
@@ -12519,10 +12531,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45693</v>
       </c>
       <c r="C64" t="n">
@@ -12556,10 +12568,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45776</v>
       </c>
       <c r="C65" t="n">
@@ -12593,10 +12605,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45870</v>
       </c>
       <c r="C66" t="n">
@@ -12630,10 +12642,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45958</v>
       </c>
       <c r="C67" t="n">
@@ -12667,10 +12679,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46057</v>
       </c>
       <c r="C68" t="n">
@@ -12704,10 +12716,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46141</v>
       </c>
       <c r="C69" t="n">
@@ -12741,10 +12753,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46233</v>
       </c>
       <c r="C70" t="n">
@@ -12796,12 +12808,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/REGN.xlsx
+++ b/salidas/empresas/REGN.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>15.08762168884277</v>
+        <v>15.08762073516846</v>
       </c>
       <c r="C2" t="n">
         <v>15.22999954223633</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>12.81902885437012</v>
+        <v>12.81902980804443</v>
       </c>
       <c r="C6" t="n">
         <v>12.9399995803833</v>
@@ -612,7 +612,7 @@
         <v>38929</v>
       </c>
       <c r="B8" t="n">
-        <v>13.53229999542236</v>
+        <v>13.53229808807373</v>
       </c>
       <c r="C8" t="n">
         <v>13.65999984741211</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>15.73154735565186</v>
+        <v>15.73154640197754</v>
       </c>
       <c r="C9" t="n">
         <v>15.88000011444092</v>
@@ -650,7 +650,7 @@
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>15.54332256317139</v>
+        <v>15.54332160949707</v>
       </c>
       <c r="C10" t="n">
         <v>15.6899995803833</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>19.8625602722168</v>
+        <v>19.86256217956543</v>
       </c>
       <c r="C11" t="n">
         <v>20.04999923706055</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>21.30891418457031</v>
+        <v>21.30891227722168</v>
       </c>
       <c r="C12" t="n">
         <v>21.51000022888184</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>19.88237380981445</v>
+        <v>19.88237190246582</v>
       </c>
       <c r="C13" t="n">
         <v>20.06999969482422</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>19.70405387878418</v>
+        <v>19.70405578613281</v>
       </c>
       <c r="C14" t="n">
         <v>19.88999938964844</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>19.65452575683594</v>
+        <v>19.65452766418457</v>
       </c>
       <c r="C15" t="n">
         <v>19.84000015258789</v>
@@ -764,7 +764,7 @@
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>21.41788482666016</v>
+        <v>21.41788291931152</v>
       </c>
       <c r="C16" t="n">
         <v>21.6200008392334</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>22.2302188873291</v>
+        <v>22.23022079467773</v>
       </c>
       <c r="C18" t="n">
         <v>22.44000053405762</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>17.75247383117676</v>
+        <v>17.75247192382812</v>
       </c>
       <c r="C19" t="n">
         <v>17.92000007629395</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>14.75080013275146</v>
+        <v>14.75080108642578</v>
       </c>
       <c r="C20" t="n">
         <v>14.89000034332275</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>17.63359832763672</v>
+        <v>17.63359451293945</v>
       </c>
       <c r="C22" t="n">
         <v>17.79999923706055</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>21.79433250427246</v>
+        <v>21.79433059692383</v>
       </c>
       <c r="C23" t="n">
         <v>22</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>21.57638931274414</v>
+        <v>21.57639122009277</v>
       </c>
       <c r="C24" t="n">
         <v>21.78000068664551</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>23.92423439025879</v>
+        <v>23.92423057556152</v>
       </c>
       <c r="C25" t="n">
         <v>24.14999961853027</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>19.58518218994141</v>
+        <v>19.58518028259277</v>
       </c>
       <c r="C27" t="n">
         <v>19.77000045776367</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>19.01060104370117</v>
+        <v>19.0106029510498</v>
       </c>
       <c r="C28" t="n">
         <v>19.19000053405762</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>14.305006980896</v>
+        <v>14.30500602722168</v>
       </c>
       <c r="C31" t="n">
         <v>14.4399995803833</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>21.68535995483398</v>
+        <v>21.68535804748535</v>
       </c>
       <c r="C32" t="n">
         <v>21.88999938964844</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>21.51694869995117</v>
+        <v>21.5169506072998</v>
       </c>
       <c r="C33" t="n">
         <v>21.71999931335449</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>15.31547164916992</v>
+        <v>15.31547260284424</v>
       </c>
       <c r="C36" t="n">
         <v>15.46000003814697</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>17.31658554077148</v>
+        <v>17.31658744812012</v>
       </c>
       <c r="C38" t="n">
         <v>17.47999954223633</v>
@@ -1277,7 +1277,7 @@
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>17.75247383117676</v>
+        <v>17.75247192382812</v>
       </c>
       <c r="C43" t="n">
         <v>17.92000007629395</v>
@@ -1353,7 +1353,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>15.55322933197021</v>
+        <v>15.55322742462158</v>
       </c>
       <c r="C47" t="n">
         <v>15.69999980926514</v>
@@ -1372,7 +1372,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>18.1784553527832</v>
+        <v>18.17845344543457</v>
       </c>
       <c r="C48" t="n">
         <v>18.35000038146973</v>
@@ -1391,7 +1391,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>23.95395660400391</v>
+        <v>23.95395469665527</v>
       </c>
       <c r="C49" t="n">
         <v>24.18000030517578</v>
@@ -1429,7 +1429,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>24.23133659362793</v>
+        <v>24.23133277893066</v>
       </c>
       <c r="C51" t="n">
         <v>24.45999908447266</v>
@@ -1448,7 +1448,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>26.24235725402832</v>
+        <v>26.24235534667969</v>
       </c>
       <c r="C52" t="n">
         <v>26.48999977111816</v>
@@ -1467,7 +1467,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>25.29133224487305</v>
+        <v>25.29133415222168</v>
       </c>
       <c r="C53" t="n">
         <v>25.53000068664551</v>
@@ -1486,7 +1486,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>28.30291175842285</v>
+        <v>28.30290985107422</v>
       </c>
       <c r="C54" t="n">
         <v>28.56999969482422</v>
@@ -1505,7 +1505,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>22.11134147644043</v>
+        <v>22.1113395690918</v>
       </c>
       <c r="C55" t="n">
         <v>22.31999969482422</v>
@@ -1524,7 +1524,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>23.96385955810547</v>
+        <v>23.96385765075684</v>
       </c>
       <c r="C56" t="n">
         <v>24.19000053405762</v>
@@ -1574,7 +1574,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>27.14384841918945</v>
+        <v>27.14385223388672</v>
       </c>
       <c r="C58" t="n">
         <v>27.39999961853027</v>
@@ -1599,7 +1599,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>25.86591339111328</v>
+        <v>25.86591148376465</v>
       </c>
       <c r="C59" t="n">
         <v>26.11000061035156</v>
@@ -1724,7 +1724,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>44.51988220214844</v>
+        <v>44.51987457275391</v>
       </c>
       <c r="C64" t="n">
         <v>44.93999862670898</v>
@@ -1749,7 +1749,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>50.56285095214844</v>
+        <v>50.5628547668457</v>
       </c>
       <c r="C65" t="n">
         <v>51.04000091552734</v>
@@ -1774,7 +1774,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>59.45890426635742</v>
+        <v>59.45890045166016</v>
       </c>
       <c r="C66" t="n">
         <v>60.02000045776367</v>
@@ -1799,7 +1799,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>56.17984390258789</v>
+        <v>56.17984771728516</v>
       </c>
       <c r="C67" t="n">
         <v>56.70999908447266</v>
@@ -1824,7 +1824,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>52.56396865844727</v>
+        <v>52.56396484375</v>
       </c>
       <c r="C68" t="n">
         <v>53.06000137329102</v>
@@ -1849,7 +1849,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>58.47815322875977</v>
+        <v>58.47815704345703</v>
       </c>
       <c r="C69" t="n">
         <v>59.02999877929688</v>
@@ -1874,7 +1874,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>57.65592193603516</v>
+        <v>57.65591430664062</v>
       </c>
       <c r="C70" t="n">
         <v>58.20000076293945</v>
@@ -1899,7 +1899,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>54.78302383422852</v>
+        <v>54.78303146362305</v>
       </c>
       <c r="C71" t="n">
         <v>55.29999923706055</v>
@@ -1924,7 +1924,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>58.86450958251953</v>
+        <v>58.86450576782227</v>
       </c>
       <c r="C72" t="n">
         <v>59.41999816894531</v>
@@ -1974,7 +1974,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>90.01058959960938</v>
+        <v>90.01059722900391</v>
       </c>
       <c r="C74" t="n">
         <v>90.86000061035156</v>
@@ -1999,7 +1999,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>103.8103790283203</v>
+        <v>103.8103713989258</v>
       </c>
       <c r="C75" t="n">
         <v>104.7900009155273</v>
@@ -2026,7 +2026,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>115.5297775268555</v>
+        <v>115.52978515625</v>
       </c>
       <c r="C76" t="n">
         <v>116.620002746582</v>
@@ -2053,7 +2053,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>133.9955139160156</v>
+        <v>133.9955291748047</v>
       </c>
       <c r="C77" t="n">
         <v>135.2599945068359</v>
@@ -2080,7 +2080,7 @@
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>134.3818969726562</v>
+        <v>134.3818664550781</v>
       </c>
       <c r="C78" t="n">
         <v>135.6499938964844</v>
@@ -2134,7 +2134,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>133.3912200927734</v>
+        <v>133.3912048339844</v>
       </c>
       <c r="C80" t="n">
         <v>134.6499938964844</v>
@@ -2161,7 +2161,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>146.6659393310547</v>
+        <v>146.6659545898438</v>
       </c>
       <c r="C81" t="n">
         <v>148.0500030517578</v>
@@ -2188,7 +2188,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>151.2328338623047</v>
+        <v>151.2328491210938</v>
       </c>
       <c r="C82" t="n">
         <v>152.6600036621094</v>
@@ -2215,7 +2215,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>140.9697265625</v>
+        <v>140.9697113037109</v>
       </c>
       <c r="C83" t="n">
         <v>142.3000030517578</v>
@@ -2242,7 +2242,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>174.8995056152344</v>
+        <v>174.8995208740234</v>
       </c>
       <c r="C84" t="n">
         <v>176.5500030517578</v>
@@ -2296,7 +2296,7 @@
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>172.3139038085938</v>
+        <v>172.3139190673828</v>
       </c>
       <c r="C86" t="n">
         <v>173.9400024414062</v>
@@ -2323,7 +2323,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>165.4387817382812</v>
+        <v>165.4387969970703</v>
       </c>
       <c r="C87" t="n">
         <v>167</v>
@@ -2352,7 +2352,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>174.7509307861328</v>
+        <v>174.7509002685547</v>
       </c>
       <c r="C88" t="n">
         <v>176.3999938964844</v>
@@ -2381,7 +2381,7 @@
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>213.1287689208984</v>
+        <v>213.1287536621094</v>
       </c>
       <c r="C89" t="n">
         <v>215.1399993896484</v>
@@ -2439,7 +2439,7 @@
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>222.7776947021484</v>
+        <v>222.7777252197266</v>
       </c>
       <c r="C91" t="n">
         <v>224.8800048828125</v>
@@ -2468,7 +2468,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>267.5353088378906</v>
+        <v>267.5353698730469</v>
       </c>
       <c r="C92" t="n">
         <v>270.0599975585938</v>
@@ -2526,7 +2526,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>309.9451293945312</v>
+        <v>309.9450988769531</v>
       </c>
       <c r="C94" t="n">
         <v>312.8699951171875</v>
@@ -2555,7 +2555,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>284.9114074707031</v>
+        <v>284.911376953125</v>
       </c>
       <c r="C95" t="n">
         <v>287.6000061035156</v>
@@ -2642,7 +2642,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>285.8921203613281</v>
+        <v>285.8920593261719</v>
       </c>
       <c r="C98" t="n">
         <v>288.5899963378906</v>
@@ -2700,7 +2700,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>297.4728698730469</v>
+        <v>297.4728393554688</v>
       </c>
       <c r="C100" t="n">
         <v>300.2799987792969</v>
@@ -2729,7 +2729,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>294.1145324707031</v>
+        <v>294.114501953125</v>
       </c>
       <c r="C101" t="n">
         <v>296.8900146484375</v>
@@ -2758,7 +2758,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>304.0903625488281</v>
+        <v>304.0903930664062</v>
       </c>
       <c r="C102" t="n">
         <v>306.9599914550781</v>
@@ -2816,7 +2816,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>313.2638244628906</v>
+        <v>313.2637939453125</v>
       </c>
       <c r="C104" t="n">
         <v>316.2200012207031</v>
@@ -2845,7 +2845,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>347.1836853027344</v>
+        <v>347.1837463378906</v>
       </c>
       <c r="C105" t="n">
         <v>350.4599914550781</v>
@@ -2874,7 +2874,7 @@
         <v>41912</v>
       </c>
       <c r="B106" t="n">
-        <v>357.1496887207031</v>
+        <v>357.149658203125</v>
       </c>
       <c r="C106" t="n">
         <v>360.5199890136719</v>
@@ -2903,7 +2903,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>390.039306640625</v>
+        <v>390.0393371582031</v>
       </c>
       <c r="C107" t="n">
         <v>393.7200012207031</v>
@@ -2961,7 +2961,7 @@
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>406.4147644042969</v>
+        <v>406.414794921875</v>
       </c>
       <c r="C109" t="n">
         <v>410.25</v>
@@ -2990,7 +2990,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>412.764892578125</v>
+        <v>412.7648620605469</v>
       </c>
       <c r="C110" t="n">
         <v>416.6600036621094</v>
@@ -3077,7 +3077,7 @@
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>453.1834106445312</v>
+        <v>453.1833801269531</v>
       </c>
       <c r="C113" t="n">
         <v>457.4599914550781</v>
@@ -3106,7 +3106,7 @@
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>507.7683410644531</v>
+        <v>507.7684020996094</v>
       </c>
       <c r="C114" t="n">
         <v>512.5599975585938</v>
@@ -3135,7 +3135,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>505.361083984375</v>
+        <v>505.3610534667969</v>
       </c>
       <c r="C115" t="n">
         <v>510.1300048828125</v>
@@ -3193,7 +3193,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>508.6995544433594</v>
+        <v>508.6995239257812</v>
       </c>
       <c r="C117" t="n">
         <v>513.5</v>
@@ -3222,7 +3222,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>460.7916259765625</v>
+        <v>460.7916564941406</v>
       </c>
       <c r="C118" t="n">
         <v>465.1400146484375</v>
@@ -3251,7 +3251,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>552.1792602539062</v>
+        <v>552.1793212890625</v>
       </c>
       <c r="C119" t="n">
         <v>557.3900146484375</v>
@@ -3280,7 +3280,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>539.40966796875</v>
+        <v>539.4097290039062</v>
       </c>
       <c r="C120" t="n">
         <v>544.5</v>
@@ -3338,7 +3338,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>416.1628112792969</v>
+        <v>416.1627807617188</v>
       </c>
       <c r="C122" t="n">
         <v>420.0899963378906</v>
@@ -3367,7 +3367,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>380.4299621582031</v>
+        <v>380.4299926757812</v>
       </c>
       <c r="C123" t="n">
         <v>384.0199890136719</v>
@@ -3483,7 +3483,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>345.9652404785156</v>
+        <v>345.9652099609375</v>
       </c>
       <c r="C127" t="n">
         <v>349.2300109863281</v>
@@ -3512,7 +3512,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>421.145751953125</v>
+        <v>421.1457214355469</v>
       </c>
       <c r="C128" t="n">
         <v>425.1199951171875</v>
@@ -3541,7 +3541,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>388.8802185058594</v>
+        <v>388.8802490234375</v>
       </c>
       <c r="C129" t="n">
         <v>392.5499877929688</v>
@@ -3599,7 +3599,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>341.7945556640625</v>
+        <v>341.7945861816406</v>
       </c>
       <c r="C131" t="n">
         <v>345.0199890136719</v>
@@ -3657,7 +3657,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>363.6582641601562</v>
+        <v>363.658203125</v>
       </c>
       <c r="C133" t="n">
         <v>367.0899963378906</v>
@@ -3715,7 +3715,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>370.0083312988281</v>
+        <v>370.0082702636719</v>
       </c>
       <c r="C135" t="n">
         <v>373.5</v>
@@ -3773,7 +3773,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>384.8582458496094</v>
+        <v>384.8581848144531</v>
       </c>
       <c r="C137" t="n">
         <v>388.489990234375</v>
@@ -3802,7 +3802,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>454.7684326171875</v>
+        <v>454.7684631347656</v>
       </c>
       <c r="C138" t="n">
         <v>459.0599975585938</v>
@@ -3831,7 +3831,7 @@
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>486.5485534667969</v>
+        <v>486.5485229492188</v>
       </c>
       <c r="C139" t="n">
         <v>491.1400146484375</v>
@@ -3860,7 +3860,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>487.0240783691406</v>
+        <v>487.0240478515625</v>
       </c>
       <c r="C140" t="n">
         <v>491.6199951171875</v>
@@ -3918,7 +3918,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>442.9401245117188</v>
+        <v>442.9400939941406</v>
       </c>
       <c r="C142" t="n">
         <v>447.1199951171875</v>
@@ -3947,7 +3947,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>398.8560485839844</v>
+        <v>398.8560791015625</v>
       </c>
       <c r="C143" t="n">
         <v>402.6199951171875</v>
@@ -4034,7 +4034,7 @@
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>363.2223510742188</v>
+        <v>363.2223815917969</v>
       </c>
       <c r="C146" t="n">
         <v>366.6499938964844</v>
@@ -4092,7 +4092,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>341.1407470703125</v>
+        <v>341.1407165527344</v>
       </c>
       <c r="C148" t="n">
         <v>344.3599853515625</v>
@@ -4121,7 +4121,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>300.8410339355469</v>
+        <v>300.841064453125</v>
       </c>
       <c r="C149" t="n">
         <v>303.6799926757812</v>
@@ -4179,7 +4179,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>341.7648620605469</v>
+        <v>341.7648315429688</v>
       </c>
       <c r="C151" t="n">
         <v>344.989990234375</v>
@@ -4237,7 +4237,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>402.9475402832031</v>
+        <v>402.9474792480469</v>
       </c>
       <c r="C153" t="n">
         <v>406.75</v>
@@ -4266,7 +4266,7 @@
         <v>43373</v>
       </c>
       <c r="B154" t="n">
-        <v>400.2628173828125</v>
+        <v>400.2628479003906</v>
       </c>
       <c r="C154" t="n">
         <v>404.0400085449219</v>
@@ -4295,7 +4295,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>336.0685729980469</v>
+        <v>336.068603515625</v>
       </c>
       <c r="C155" t="n">
         <v>339.239990234375</v>
@@ -4353,7 +4353,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>370.0083312988281</v>
+        <v>370.0082702636719</v>
       </c>
       <c r="C157" t="n">
         <v>373.5</v>
@@ -4411,7 +4411,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>426.7131652832031</v>
+        <v>426.7132263183594</v>
       </c>
       <c r="C159" t="n">
         <v>430.739990234375</v>
@@ -4440,7 +4440,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>406.7812805175781</v>
+        <v>406.7813415527344</v>
       </c>
       <c r="C160" t="n">
         <v>410.6199951171875</v>
@@ -4469,7 +4469,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>339.93212890625</v>
+        <v>339.9321594238281</v>
       </c>
       <c r="C161" t="n">
         <v>343.1400146484375</v>
@@ -4556,7 +4556,7 @@
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>301.9109802246094</v>
+        <v>301.9109191894531</v>
       </c>
       <c r="C164" t="n">
         <v>304.760009765625</v>
@@ -4643,7 +4643,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>303.4167175292969</v>
+        <v>303.416748046875</v>
       </c>
       <c r="C167" t="n">
         <v>306.2799987792969</v>
@@ -4701,7 +4701,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>371.9698181152344</v>
+        <v>371.9698486328125</v>
       </c>
       <c r="C169" t="n">
         <v>375.4800109863281</v>
@@ -4730,7 +4730,7 @@
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>334.7807312011719</v>
+        <v>334.7807922363281</v>
       </c>
       <c r="C170" t="n">
         <v>337.9400024414062</v>
@@ -4759,7 +4759,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>440.4139404296875</v>
+        <v>440.4139709472656</v>
       </c>
       <c r="C171" t="n">
         <v>444.5700073242188</v>
@@ -4788,7 +4788,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>483.7252502441406</v>
+        <v>483.7252197265625</v>
       </c>
       <c r="C172" t="n">
         <v>488.2900085449219</v>
@@ -4817,7 +4817,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>520.9638061523438</v>
+        <v>520.9637451171875</v>
       </c>
       <c r="C173" t="n">
         <v>525.8800048828125</v>
@@ -4846,7 +4846,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>607.0811157226562</v>
+        <v>607.0811767578125</v>
       </c>
       <c r="C174" t="n">
         <v>612.8099975585938</v>
@@ -4904,7 +4904,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>626.1611938476562</v>
+        <v>626.1611328125</v>
       </c>
       <c r="C176" t="n">
         <v>632.0700073242188</v>
@@ -4962,7 +4962,7 @@
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>554.5469970703125</v>
+        <v>554.5469360351562</v>
       </c>
       <c r="C178" t="n">
         <v>559.780029296875</v>
@@ -4991,7 +4991,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>538.4784545898438</v>
+        <v>538.478515625</v>
       </c>
       <c r="C179" t="n">
         <v>543.5599975585938</v>
@@ -5020,7 +5020,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>511.2059631347656</v>
+        <v>511.2058715820312</v>
       </c>
       <c r="C180" t="n">
         <v>516.030029296875</v>
@@ -5049,7 +5049,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>478.5936584472656</v>
+        <v>478.5936279296875</v>
       </c>
       <c r="C181" t="n">
         <v>483.1099853515625</v>
@@ -5107,7 +5107,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>446.3578491210938</v>
+        <v>446.35791015625</v>
       </c>
       <c r="C183" t="n">
         <v>450.5700073242188</v>
@@ -5136,7 +5136,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>468.7168579101562</v>
+        <v>468.7168273925781</v>
       </c>
       <c r="C184" t="n">
         <v>473.1400146484375</v>
@@ -5165,7 +5165,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>476.800537109375</v>
+        <v>476.8005676269531</v>
       </c>
       <c r="C185" t="n">
         <v>481.2999877929688</v>
@@ -5194,7 +5194,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>497.7330017089844</v>
+        <v>497.7330322265625</v>
       </c>
       <c r="C186" t="n">
         <v>502.4299926757812</v>
@@ -5397,7 +5397,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>625.6162719726562</v>
+        <v>625.6161499023438</v>
       </c>
       <c r="C193" t="n">
         <v>631.52001953125</v>
@@ -5426,7 +5426,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>602.900634765625</v>
+        <v>602.9005737304688</v>
       </c>
       <c r="C194" t="n">
         <v>608.5900268554688</v>
@@ -5484,7 +5484,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>691.890869140625</v>
+        <v>691.8908081054688</v>
       </c>
       <c r="C196" t="n">
         <v>698.4199829101562</v>
@@ -5542,7 +5542,7 @@
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>658.525634765625</v>
+        <v>658.5256958007812</v>
       </c>
       <c r="C198" t="n">
         <v>664.739990234375</v>
@@ -5571,7 +5571,7 @@
         <v>44742</v>
       </c>
       <c r="B199" t="n">
-        <v>585.6038208007812</v>
+        <v>585.6038818359375</v>
       </c>
       <c r="C199" t="n">
         <v>591.1300048828125</v>
@@ -5600,7 +5600,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>576.2521362304688</v>
+        <v>576.2520751953125</v>
       </c>
       <c r="C200" t="n">
         <v>581.6900024414062</v>
@@ -5629,7 +5629,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>575.6279907226562</v>
+        <v>575.6278686523438</v>
       </c>
       <c r="C201" t="n">
         <v>581.0599975585938</v>
@@ -5716,7 +5716,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>744.6727905273438</v>
+        <v>744.6726684570312</v>
       </c>
       <c r="C204" t="n">
         <v>751.7000122070312</v>
@@ -5745,7 +5745,7 @@
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>714.7451782226562</v>
+        <v>714.7450561523438</v>
       </c>
       <c r="C205" t="n">
         <v>721.489990234375</v>
@@ -5803,7 +5803,7 @@
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>753.3111572265625</v>
+        <v>753.3112182617188</v>
       </c>
       <c r="C207" t="n">
         <v>760.4199829101562</v>
@@ -5861,7 +5861,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>794.29443359375</v>
+        <v>794.2943725585938</v>
       </c>
       <c r="C209" t="n">
         <v>801.7899780273438</v>
@@ -5890,7 +5890,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>728.6836547851562</v>
+        <v>728.68359375</v>
       </c>
       <c r="C210" t="n">
         <v>735.5599975585938</v>
@@ -5948,7 +5948,7 @@
         <v>45138</v>
       </c>
       <c r="B212" t="n">
-        <v>734.9741821289062</v>
+        <v>734.9742431640625</v>
       </c>
       <c r="C212" t="n">
         <v>741.9099731445312</v>
@@ -5977,7 +5977,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>818.7634887695312</v>
+        <v>818.7635498046875</v>
       </c>
       <c r="C213" t="n">
         <v>826.489990234375</v>
@@ -6006,7 +6006,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>815.2664794921875</v>
+        <v>815.2666625976562</v>
       </c>
       <c r="C214" t="n">
         <v>822.9600219726562</v>
@@ -6064,7 +6064,7 @@
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>816.1085815429688</v>
+        <v>816.108642578125</v>
       </c>
       <c r="C216" t="n">
         <v>823.8099975585938</v>
@@ -6093,7 +6093,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>870.0792236328125</v>
+        <v>870.0792846679688</v>
       </c>
       <c r="C217" t="n">
         <v>878.2899780273438</v>
@@ -6122,7 +6122,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>933.9664916992188</v>
+        <v>933.9664306640625</v>
       </c>
       <c r="C218" t="n">
         <v>942.780029296875</v>
@@ -6151,7 +6151,7 @@
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>957.0585327148438</v>
+        <v>957.0584716796875</v>
       </c>
       <c r="C219" t="n">
         <v>966.0900268554688</v>
@@ -6238,7 +6238,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>970.9968872070312</v>
+        <v>970.9969482421875</v>
       </c>
       <c r="C222" t="n">
         <v>980.1599731445312</v>
@@ -6267,7 +6267,7 @@
         <v>45473</v>
       </c>
       <c r="B223" t="n">
-        <v>1041.204467773438</v>
+        <v>1041.20458984375</v>
       </c>
       <c r="C223" t="n">
         <v>1051.030029296875</v>
@@ -6296,7 +6296,7 @@
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>1069.100952148438</v>
+        <v>1069.101196289062</v>
       </c>
       <c r="C224" t="n">
         <v>1079.18994140625</v>
@@ -6354,7 +6354,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>1041.41259765625</v>
+        <v>1041.412475585938</v>
       </c>
       <c r="C226" t="n">
         <v>1051.239990234375</v>
@@ -6470,7 +6470,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>666.6886596679688</v>
+        <v>666.688720703125</v>
       </c>
       <c r="C230" t="n">
         <v>672.97998046875</v>
@@ -6615,7 +6615,7 @@
         <v>45838</v>
       </c>
       <c r="B235" t="n">
-        <v>521.5297241210938</v>
+        <v>521.52978515625</v>
       </c>
       <c r="C235" t="n">
         <v>525</v>
@@ -6644,7 +6644,7 @@
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>541.8544921875</v>
+        <v>541.8545532226562</v>
       </c>
       <c r="C236" t="n">
         <v>545.4600219726562</v>
@@ -6673,7 +6673,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>577.737548828125</v>
+        <v>577.7374877929688</v>
       </c>
       <c r="C237" t="n">
         <v>580.7000122070312</v>
@@ -6702,7 +6702,7 @@
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>559.4014892578125</v>
+        <v>559.4015502929688</v>
       </c>
       <c r="C238" t="n">
         <v>562.27001953125</v>
@@ -6760,7 +6760,7 @@
         <v>45991</v>
       </c>
       <c r="B240" t="n">
-        <v>777.1829223632812</v>
+        <v>777.1829833984375</v>
       </c>
       <c r="C240" t="n">
         <v>780.1900024414062</v>
@@ -6847,7 +6847,7 @@
         <v>46081</v>
       </c>
       <c r="B243" t="n">
-        <v>779.5938720703125</v>
+        <v>779.5939331054688</v>
       </c>
       <c r="C243" t="n">
         <v>781.6699829101562</v>
